--- a/cp-short-description/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/cp-short-description/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:20:15+00:00</t>
+    <t>2026-06-25T15:53:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/cp-short-description/ig/StructureDefinition-pdsm-find-lists-response.xlsx
+++ b/cp-short-description/ig/StructureDefinition-pdsm-find-lists-response.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:53:08+00:00</t>
+    <t>2026-06-25T16:02:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
